--- a/output/mia_historico.xlsx
+++ b/output/mia_historico.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,52 +418,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sub_Ejecutivo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sub_Legislativo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>sub_Judicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sub_Prensa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sub_Banco Central</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cobertura_vars</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>actualizado</t>
         </is>
@@ -1666,34 +1654,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.5151080258649</v>
+        <v>54.80453446587981</v>
       </c>
       <c r="C33" t="n">
-        <v>50.80625411713648</v>
+        <v>51.44056037041607</v>
       </c>
       <c r="D33" t="n">
-        <v>46.67377851678921</v>
+        <v>48.03511791476498</v>
       </c>
       <c r="E33" t="n">
-        <v>44.94500366300366</v>
+        <v>45.18131318681319</v>
       </c>
       <c r="F33" t="n">
-        <v>71.51421739130434</v>
+        <v>71.48534782608695</v>
       </c>
       <c r="G33" t="n">
-        <v>68.1489516404648</v>
+        <v>66.70851973684211</v>
       </c>
       <c r="H33" t="n">
         <v>18</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-19 10:04</t>
+          <t>2026-09-17 15:24</t>
         </is>
       </c>
     </row>
@@ -1712,107 +1700,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DNU vs Leyes</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Discrecionalidad presup.</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Transparencia (AIP)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ATN (federalismo)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Eficacia de Control</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Calidad Normativa</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Costo del Legislativo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Desempeño de la Corte</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cobertura Judicial</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Escrutinio Abierto</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Pauta Publicitaria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Causas contra periodistas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Medios estatales</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Acceso de la prensa</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Financiamiento al Tesoro</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Letras intransferibles</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Designación Pdte. BCRA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Respeto Carta Orgánica</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actualizado</t>
         </is>
@@ -4022,13 +4010,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="C33" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>65.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>81.3</v>
@@ -4037,16 +4025,16 @@
         <v>20.9</v>
       </c>
       <c r="G33" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>73.5</v>
+        <v>83.3</v>
       </c>
       <c r="I33" t="n">
         <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>67.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K33" t="n">
         <v>100</v>
@@ -4058,16 +4046,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="O33" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>68.2</v>
+        <v>62.3</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4077,12 +4065,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-08-19 10:04</t>
+          <t>2026-09-17 15:24</t>
         </is>
       </c>
     </row>
